--- a/data/Dungeon.xlsx
+++ b/data/Dungeon.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -437,6 +437,11 @@
           <t>time_limit</t>
         </is>
       </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>monster</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -459,6 +464,11 @@
           <t>uint32</t>
         </is>
       </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>repeated uint32</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -481,26 +491,35 @@
           <t>common</t>
         </is>
       </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
           <t>fk:BaseScene</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>fk:Monster</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
           <t>FK -&gt; BaseScene.id</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>本副本刷新的怪物 id 列表</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -515,6 +534,12 @@
       <c r="D6" t="n">
         <v>1800</v>
       </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -529,6 +554,12 @@
       <c r="D7" t="n">
         <v>3600</v>
       </c>
+      <c r="E7" t="n">
+        <v>6</v>
+      </c>
+      <c r="F7" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -542,6 +573,15 @@
       </c>
       <c r="D8" t="n">
         <v>1800</v>
+      </c>
+      <c r="E8" t="n">
+        <v>11</v>
+      </c>
+      <c r="F8" t="n">
+        <v>12</v>
+      </c>
+      <c r="G8" t="n">
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/data/Dungeon.xlsx
+++ b/data/Dungeon.xlsx
@@ -438,69 +438,15 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>uint32</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>uint32</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>uint32</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>uint32</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr"/>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>fk:BaseScene</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-    </row>
+    <row r="2"/>
+    <row r="3"/>
+    <row r="4"/>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
           <t>FK -&gt; BaseScene.id</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
